--- a/performance-testing/results.xlsx
+++ b/performance-testing/results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrei/Developer/tweebyte/performance-testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE08E860-ACC0-9B48-BF2C-5953C5670AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C931BA-9FB9-7A44-A447-F0D75B41E97D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="3" xr2:uid="{B98ED615-AEA2-8C4F-96EB-75A81CB30B52}"/>
+    <workbookView xWindow="4220" yWindow="1140" windowWidth="16880" windowHeight="14200" activeTab="3" xr2:uid="{B98ED615-AEA2-8C4F-96EB-75A81CB30B52}"/>
   </bookViews>
   <sheets>
     <sheet name="User Summary GET" sheetId="1" r:id="rId1"/>
